--- a/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3CF4999-E3EF-4DFE-B6D7-C5D8D4E13EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA73E75C-AC76-4E43-9C1C-7C12DB6362EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960EF684-5487-4BA1-BCE3-407ED7148482}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{108AA3FF-40B9-465A-9B35-DB737CEA713A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3524,7 +3524,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA0C626B-EBBD-4D95-9F1B-F186571D9AB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB0F4F6A-5974-47B4-9A0F-0859711AC1B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,7 +3582,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B31547-F384-42FA-9146-53A059FEFA01}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5AAEE5D-D0AD-44E7-A59C-550A80BEBB74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3640,7 +3640,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CCD8BE6-31A0-4B90-BB74-7A4D56BA1DDE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25D4BAB0-D534-40DC-AF67-AAEB1795C3E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3698,7 +3698,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B6724DD-AC8B-420B-A695-69FC9EC8A0BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D074B9DB-3757-44E7-B274-37F0F3E43176}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3756,7 +3756,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3079180-C919-45B3-92DE-10A590CC5EC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21D466A4-043C-4AAA-9267-05601DF59B6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3814,7 +3814,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92760D89-4E60-4EB0-8959-3FC4554D1641}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B36E7A4-C7B7-45D7-83B9-F6C14D01D6DA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3874,7 +3874,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7486C6-71AF-4278-9558-F8CD57F14274}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1454A11C-605E-483E-BCFC-D4A0CCEC9382}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3932,7 +3932,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{344FC547-693F-4520-9421-D008F325BF26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49839BC5-B3E0-4FF4-BF93-AEE61EBA2E5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3990,7 +3990,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D75227-3FF5-4F97-976E-2894274D09BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5EA0E2-373C-4281-BCAA-C5817D5764A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4050,7 +4050,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94232357-8D62-4168-AE02-E4365F970EEB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{537893F6-4B52-4DEA-BC48-E75B2CD201AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4106,7 +4106,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63D0C2ED-7939-4105-9CC8-C19423A32E12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E46CF5-6298-4504-8150-8AED73EB3632}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4164,7 +4164,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{282C5B3C-151A-4D31-BACA-FDA799FE32A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E43537-DEF5-42F5-939D-F08D3B63FC98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4222,7 +4222,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28A2A9D-A83C-4B3F-A8F8-49514F21F240}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE53C637-C340-42CC-B06D-0DF7BBA74C19}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4282,7 +4282,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CE1C389-EDC6-49E5-8026-B3C103FE44C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D6C6EAA-10E5-43A7-AECF-1C8FEB5B4B96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4338,7 +4338,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE55BC84-F9AB-4511-A098-E92DF0505548}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0E12BA-E0DC-425F-95F1-6D1E95BF7B09}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4394,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3CC50B8-343B-441A-8B01-EEC531B7C1A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43BF27ED-BB5F-42F6-8DC5-EB548A3FF194}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4452,7 +4452,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9972F874-A750-434D-83DA-BFB68543734D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3462A1D5-7170-4C47-81C9-8CDBF9FE80A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4510,7 +4510,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB19993-DDCB-45D9-A955-937BE537A1E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B77BDD-C7CD-4C7F-8669-26FF398D94EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4841,7 +4841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE789C8-397B-4A2C-B282-CF477AB9D13C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9678ECFC-4251-4881-BAA1-69DC97AFC659}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5553,7 +5553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631A0E03-6E06-4E8A-BE23-B4FB6D546418}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DE84B2-AB23-4761-A08E-EBCE0D8C6776}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6884,7 +6884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7458FA41-E6E8-4F46-BED3-6C77B9C11B29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7F5B48-C0CD-4C66-BE3B-0B19ED2AB7DC}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7014,7 +7014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14167F7A-7BD6-4DD7-B5D1-E5856798C28E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D77479-878F-498D-B307-DE9062132DE6}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA73E75C-AC76-4E43-9C1C-7C12DB6362EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8F53593-67EB-4FC2-B78C-602E41BF139B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{108AA3FF-40B9-465A-9B35-DB737CEA713A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD3AAD7-B834-446F-9E69-9158BF646FBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3524,7 +3524,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB0F4F6A-5974-47B4-9A0F-0859711AC1B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D48240D-7DEF-4614-8106-87D1A54AC581}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,7 +3582,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5AAEE5D-D0AD-44E7-A59C-550A80BEBB74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD96735-25AB-40A0-AF73-BB8D01F83014}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3640,7 +3640,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25D4BAB0-D534-40DC-AF67-AAEB1795C3E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23686968-6607-4B5F-BCFE-12C72F92D934}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3698,7 +3698,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D074B9DB-3757-44E7-B274-37F0F3E43176}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51F76FE2-BD25-4CA4-97BE-BC8CE70DE783}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3756,7 +3756,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21D466A4-043C-4AAA-9267-05601DF59B6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0710C97B-48B8-4EF3-8B11-98B2A29EC02B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3814,7 +3814,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B36E7A4-C7B7-45D7-83B9-F6C14D01D6DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFFDB0EA-AAEB-47BD-A925-D0E27426EDD3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3874,7 +3874,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1454A11C-605E-483E-BCFC-D4A0CCEC9382}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0FB2D34-A8B5-4035-8654-DC5821BDCD18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3932,7 +3932,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49839BC5-B3E0-4FF4-BF93-AEE61EBA2E5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F897BBE-32A8-4D86-9DAB-23DDE3B4318F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3990,7 +3990,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5EA0E2-373C-4281-BCAA-C5817D5764A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C9BD955-8497-4090-8ABF-8728D3F37A8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4050,7 +4050,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{537893F6-4B52-4DEA-BC48-E75B2CD201AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6F0779F-CDC3-4D20-8E1C-B5643BA1E4F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4106,7 +4106,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E46CF5-6298-4504-8150-8AED73EB3632}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54D77BDF-097D-4AB4-A321-012847A6D82F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4164,7 +4164,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E43537-DEF5-42F5-939D-F08D3B63FC98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E2F75D-1097-4B7F-97B7-7C45379B6EDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4222,7 +4222,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE53C637-C340-42CC-B06D-0DF7BBA74C19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB10AAA3-7CA7-4BA4-AA21-60436B855D89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4282,7 +4282,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D6C6EAA-10E5-43A7-AECF-1C8FEB5B4B96}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542254BF-36CE-4606-8962-A2A027ABCB6D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4338,7 +4338,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0E12BA-E0DC-425F-95F1-6D1E95BF7B09}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B639679-7588-462B-873E-23945C72F0E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4394,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43BF27ED-BB5F-42F6-8DC5-EB548A3FF194}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EC227FE-D34B-43F7-AF87-C78E9E2540DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4452,7 +4452,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3462A1D5-7170-4C47-81C9-8CDBF9FE80A4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74602C85-4B00-4CF0-94D4-519B87ABF896}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4510,7 +4510,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B77BDD-C7CD-4C7F-8669-26FF398D94EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27283207-DFC5-4200-9A22-E754724E1E73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4841,7 +4841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9678ECFC-4251-4881-BAA1-69DC97AFC659}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C9BC90-BF18-49BD-958A-FB7BF03D380A}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5553,7 +5553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DE84B2-AB23-4761-A08E-EBCE0D8C6776}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5E0B5A-95AC-4589-81FF-3727B44D4C57}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6884,7 +6884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7F5B48-C0CD-4C66-BE3B-0B19ED2AB7DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2C49FE-F4CB-4B6E-8F9F-4DD54170F740}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7014,7 +7014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D77479-878F-498D-B307-DE9062132DE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49943AC4-A2B2-4830-A6E8-B4682866B534}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8F53593-67EB-4FC2-B78C-602E41BF139B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C4AECF7-1649-4E3B-8B56-A11A79DE059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD3AAD7-B834-446F-9E69-9158BF646FBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00704FA1-4FE6-4498-88AC-6F80BDE31A6B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3524,7 +3524,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D48240D-7DEF-4614-8106-87D1A54AC581}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0CABDE3-1396-49E2-BAD1-8F02982E46BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,7 +3582,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD96735-25AB-40A0-AF73-BB8D01F83014}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16DA31F1-2FEE-444F-9C18-1291D1C28533}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3640,7 +3640,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23686968-6607-4B5F-BCFE-12C72F92D934}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64460905-4CC5-40E3-AC85-A689AACDA398}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3698,7 +3698,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51F76FE2-BD25-4CA4-97BE-BC8CE70DE783}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F43844E-B5E7-4949-B7F9-B1926C6FA5DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3756,7 +3756,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0710C97B-48B8-4EF3-8B11-98B2A29EC02B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE44581B-A1AA-4979-8491-ED9AD335D4F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3814,7 +3814,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFFDB0EA-AAEB-47BD-A925-D0E27426EDD3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19BACB9F-5C61-4FD7-B22C-BF5CFB8A04FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3874,7 +3874,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0FB2D34-A8B5-4035-8654-DC5821BDCD18}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B9633AE-60BD-44AE-8BAA-7EFEA0BE930B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3932,7 +3932,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F897BBE-32A8-4D86-9DAB-23DDE3B4318F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00A5310E-DFF9-4584-A563-CA58E9557297}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3990,7 +3990,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C9BD955-8497-4090-8ABF-8728D3F37A8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53DB8AA4-BDCB-4E25-AAB9-CC206962A77B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4050,7 +4050,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6F0779F-CDC3-4D20-8E1C-B5643BA1E4F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D61EF7-A808-4BBF-B75F-65F52BFB4CCE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4106,7 +4106,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54D77BDF-097D-4AB4-A321-012847A6D82F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DE1A0E5-BD72-409A-9CCD-B2D25546BAD8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4164,7 +4164,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E2F75D-1097-4B7F-97B7-7C45379B6EDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4220B650-87FE-46A7-88E7-DD96D94D9351}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4222,7 +4222,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB10AAA3-7CA7-4BA4-AA21-60436B855D89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457B7ADB-9405-44AD-B536-D7736AC1C2FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4282,7 +4282,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542254BF-36CE-4606-8962-A2A027ABCB6D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F948D666-5C6E-4962-A76D-4F05246620B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4338,7 +4338,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B639679-7588-462B-873E-23945C72F0E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10061F0-DF75-42B1-BE15-26DDC3A5EB7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4394,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EC227FE-D34B-43F7-AF87-C78E9E2540DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A54C69-8D2B-4ADA-8149-C9E088E617ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4452,7 +4452,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74602C85-4B00-4CF0-94D4-519B87ABF896}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86453E59-7384-4D00-894D-3D1696939A26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4510,7 +4510,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27283207-DFC5-4200-9A22-E754724E1E73}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{952C007D-D99D-4883-9873-E73807D088DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4841,7 +4841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C9BC90-BF18-49BD-958A-FB7BF03D380A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86CA1B3-B2C7-4C7A-9511-F334CFBDD7BD}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5553,7 +5553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5E0B5A-95AC-4589-81FF-3727B44D4C57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84A9CA1-82AF-444D-A06C-E9F5D844EC18}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6884,7 +6884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2C49FE-F4CB-4B6E-8F9F-4DD54170F740}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60484715-BCB6-4D73-AC26-BD235EDFE285}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7014,7 +7014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49943AC4-A2B2-4830-A6E8-B4682866B534}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BAED9D-EFC4-44E5-9A9A-68BB17A42934}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>

--- a/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
+++ b/.claude/docs/Example橋脚4/post/線路方向_Aggre-SE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C4AECF7-1649-4E3B-8B56-A11A79DE059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A5DD207-1802-4E8A-9412-DCD1654FA28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
         <xdr:cNvPr id="2" name="図形 2" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00704FA1-4FE6-4498-88AC-6F80BDE31A6B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E61E3482-677C-417B-A380-9B100F1B5F29}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3524,7 +3524,7 @@
         <xdr:cNvPr id="3" name="図形 3" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0CABDE3-1396-49E2-BAD1-8F02982E46BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D1CCCA8-6584-4413-9EC6-1A04E5D34765}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,7 +3582,7 @@
         <xdr:cNvPr id="4" name="図形 4" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16DA31F1-2FEE-444F-9C18-1291D1C28533}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B126717D-8D43-45C9-9212-7928E596ED3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3640,7 +3640,7 @@
         <xdr:cNvPr id="5" name="図形 5" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64460905-4CC5-40E3-AC85-A689AACDA398}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4979BF75-AEBF-49E7-9720-1C05CEF2E9DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3698,7 +3698,7 @@
         <xdr:cNvPr id="6" name="図形 6" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F43844E-B5E7-4949-B7F9-B1926C6FA5DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{748298AD-1A50-422A-8379-9C0EA9DDCCE7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3756,7 +3756,7 @@
         <xdr:cNvPr id="7" name="図形 7" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE44581B-A1AA-4979-8491-ED9AD335D4F9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B2B8DAD-CB90-4CA2-8947-25D8F2B1C033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3814,7 +3814,7 @@
         <xdr:cNvPr id="8" name="図形 8" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19BACB9F-5C61-4FD7-B22C-BF5CFB8A04FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9472D1-A973-4F08-A4D4-C2A8876BF200}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3874,7 +3874,7 @@
         <xdr:cNvPr id="9" name="図形 9" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B9633AE-60BD-44AE-8BAA-7EFEA0BE930B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4E4B180-B809-45CD-9C78-9F7481D25DD1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3932,7 +3932,7 @@
         <xdr:cNvPr id="10" name="図形 10" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00A5310E-DFF9-4584-A563-CA58E9557297}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FDC9815-D7AA-4A64-8CB3-C665ABD4A34D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3990,7 +3990,7 @@
         <xdr:cNvPr id="11" name="図形 11" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53DB8AA4-BDCB-4E25-AAB9-CC206962A77B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A34A34A3-64DF-4AD0-BB0C-44117811D172}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4050,7 +4050,7 @@
         <xdr:cNvPr id="12" name="図形 12" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D61EF7-A808-4BBF-B75F-65F52BFB4CCE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F3FFB6E-1BE4-4935-B3A1-978161B5A942}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4106,7 +4106,7 @@
         <xdr:cNvPr id="13" name="図形 13" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DE1A0E5-BD72-409A-9CCD-B2D25546BAD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59B60574-0199-4169-BE62-6D75BBDEF1F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4164,7 +4164,7 @@
         <xdr:cNvPr id="14" name="図形 14" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4220B650-87FE-46A7-88E7-DD96D94D9351}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1857B1A-7728-4DA7-BE6D-07E8EC43C6F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4222,7 +4222,7 @@
         <xdr:cNvPr id="15" name="図形 15" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457B7ADB-9405-44AD-B536-D7736AC1C2FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC5380B-2546-4D33-A519-3A2A5E5E0072}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4282,7 +4282,7 @@
         <xdr:cNvPr id="16" name="図形 16" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F948D666-5C6E-4962-A76D-4F05246620B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDA79DBC-137B-49A9-BBE4-90D6CD450559}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4338,7 +4338,7 @@
         <xdr:cNvPr id="17" name="図形 17" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10061F0-DF75-42B1-BE15-26DDC3A5EB7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCDE22F6-3020-45FF-9149-362C4D9A20EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4394,7 @@
         <xdr:cNvPr id="18" name="図形 18" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A54C69-8D2B-4ADA-8149-C9E088E617ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68EAAAB1-DE5D-4191-AC75-AA068A9A3694}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4452,7 +4452,7 @@
         <xdr:cNvPr id="19" name="図形 19" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86453E59-7384-4D00-894D-3D1696939A26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B014C454-F8CB-4A17-A3D2-50A995B7ED98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4510,7 +4510,7 @@
         <xdr:cNvPr id="20" name="図形 20" descr="NoName.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{952C007D-D99D-4883-9873-E73807D088DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1229286-616B-478E-A280-DC47CA9D2FF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4841,7 +4841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86CA1B3-B2C7-4C7A-9511-F334CFBDD7BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{162D3B7C-A3C4-442F-90A9-A8FFBAF103CC}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5553,7 +5553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84A9CA1-82AF-444D-A06C-E9F5D844EC18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B592BD08-0EA8-4B69-A768-C3B0E963ED24}">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6884,7 +6884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60484715-BCB6-4D73-AC26-BD235EDFE285}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842FA4C4-E004-4EFF-9C8E-1AC123F55E76}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7014,7 +7014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BAED9D-EFC4-44E5-9A9A-68BB17A42934}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECFA5AF-C2EB-4AE8-B34F-B3029C67C064}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
